--- a/ig/DM-37/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="297">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -342,7 +342,7 @@
     <t>40</t>
   </si>
   <si>
-    <t>Maison d'accueil spécialisé (MAS)</t>
+    <t>Maison d'accueil spécialisée (MAS)</t>
   </si>
   <si>
     <t>41</t>
@@ -432,7 +432,7 @@
     <t>56</t>
   </si>
   <si>
-    <t>Unité d'enseignement externe</t>
+    <t>Unité d'enseignement externalisée</t>
   </si>
   <si>
     <t>57</t>
@@ -841,6 +841,60 @@
   </si>
   <si>
     <t>Unité de soins intensifs (USI) de spécialité</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Centre de protection maternelle et infantile (PMI)</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Structure Douleur Chronique (SDC)</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Centre régional du psychotraumatisme (CRP)</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Unité d'hospitalisation à domicile socle</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Unité d'hospitalisation à domicile ante et post-partum</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Unité d'hospitalisation à domicile réadaptation</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Unité d'hospitalisation à domicile enfants de moins de trois ans</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Service autonomie à domicile (SAD) aide et soins</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>Service autonomie à domicile (SAD) aide</t>
   </si>
   <si>
     <t/>
@@ -1119,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B126"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2123,15 +2177,87 @@
         <v>276</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
